--- a/artfynd/A 39577-2024 artfynd.xlsx
+++ b/artfynd/A 39577-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1980,6 +1980,830 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120099930</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>338721</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6433368</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2 m väster om stora stigen.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120100182</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>338565</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6433423</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spillkråkehack vid basen av en tallhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120100010</v>
+      </c>
+      <c r="B15" t="n">
+        <v>96175</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>338736</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6433400</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120100076</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58164</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>338703</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6433399</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ett fjolårsexemplar hoppade fram relativt nära bäcken. Troligtvis åkergroda att döma av spetsiga nosen, annars vanlig groda.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120099883</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96175</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>338748</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6433381</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120100253</v>
+      </c>
+      <c r="B18" t="n">
+        <v>84211</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3518</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Smal svampklubba</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tolypocladium ophioglossoides</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>338708</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6433322</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>I granskog ca 50-60 m norr om Gäddevadsbäckens östra gren.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120100036</v>
+      </c>
+      <c r="B19" t="n">
+        <v>96175</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>338726</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6433399</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>15 m väster om bäcken.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39577-2024 artfynd.xlsx
+++ b/artfynd/A 39577-2024 artfynd.xlsx
@@ -1982,10 +1982,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120099930</v>
+        <v>120100182</v>
       </c>
       <c r="B13" t="n">
-        <v>90334</v>
+        <v>57326</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1994,38 +1994,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2033,10 +2030,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338721</v>
+        <v>338565</v>
       </c>
       <c r="R13" t="n">
-        <v>6433368</v>
+        <v>6433423</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2073,7 +2070,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2 m väster om stora stigen.</t>
+          <t>Spillkråkehack vid basen av en tallhögstubbe.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2082,7 +2079,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2101,10 +2097,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120100182</v>
+        <v>120100076</v>
       </c>
       <c r="B14" t="n">
-        <v>57326</v>
+        <v>58164</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2113,35 +2109,40 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>208250</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2149,10 +2150,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338565</v>
+        <v>338703</v>
       </c>
       <c r="R14" t="n">
-        <v>6433423</v>
+        <v>6433399</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2189,7 +2190,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen av en tallhögstubbe.</t>
+          <t>Ett fjolårsexemplar hoppade fram relativt nära bäcken. Troligtvis åkergroda att döma av spetsiga nosen, annars vanlig groda.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2198,6 +2199,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2216,7 +2218,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120100010</v>
+        <v>120100036</v>
       </c>
       <c r="B15" t="n">
         <v>96175</v>
@@ -2251,12 +2253,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -2268,10 +2270,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338736</v>
+        <v>338726</v>
       </c>
       <c r="R15" t="n">
-        <v>6433400</v>
+        <v>6433399</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2304,6 +2306,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>15 m väster om bäcken.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2331,10 +2338,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120100076</v>
+        <v>120100253</v>
       </c>
       <c r="B16" t="n">
-        <v>58164</v>
+        <v>84211</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2347,36 +2354,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208250</v>
+        <v>3518</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2384,10 +2389,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338703</v>
+        <v>338708</v>
       </c>
       <c r="R16" t="n">
-        <v>6433399</v>
+        <v>6433322</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2424,7 +2429,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ett fjolårsexemplar hoppade fram relativt nära bäcken. Troligtvis åkergroda att döma av spetsiga nosen, annars vanlig groda.</t>
+          <t>I granskog ca 50-60 m norr om Gäddevadsbäckens östra gren.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2452,10 +2457,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120099883</v>
+        <v>120099930</v>
       </c>
       <c r="B17" t="n">
-        <v>96175</v>
+        <v>90334</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2468,35 +2473,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2569</v>
+        <v>3215</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2504,10 +2508,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338748</v>
+        <v>338721</v>
       </c>
       <c r="R17" t="n">
-        <v>6433381</v>
+        <v>6433368</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2540,6 +2544,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2 m väster om stora stigen.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2567,10 +2576,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120100253</v>
+        <v>120100010</v>
       </c>
       <c r="B18" t="n">
-        <v>84211</v>
+        <v>96175</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2583,34 +2592,35 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3518</v>
+        <v>2569</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2618,10 +2628,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338708</v>
+        <v>338736</v>
       </c>
       <c r="R18" t="n">
-        <v>6433322</v>
+        <v>6433400</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2654,11 +2664,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>I granskog ca 50-60 m norr om Gäddevadsbäckens östra gren.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2686,7 +2691,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120100036</v>
+        <v>120099883</v>
       </c>
       <c r="B19" t="n">
         <v>96175</v>
@@ -2726,7 +2731,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2738,10 +2743,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>338726</v>
+        <v>338748</v>
       </c>
       <c r="R19" t="n">
-        <v>6433399</v>
+        <v>6433381</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2774,11 +2779,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>15 m väster om bäcken.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 39577-2024 artfynd.xlsx
+++ b/artfynd/A 39577-2024 artfynd.xlsx
@@ -2218,10 +2218,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120100036</v>
+        <v>120100253</v>
       </c>
       <c r="B15" t="n">
-        <v>96175</v>
+        <v>84211</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2234,35 +2234,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2569</v>
+        <v>3518</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2270,10 +2269,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338726</v>
+        <v>338708</v>
       </c>
       <c r="R15" t="n">
-        <v>6433399</v>
+        <v>6433322</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2310,7 +2309,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>15 m väster om bäcken.</t>
+          <t>I granskog ca 50-60 m norr om Gäddevadsbäckens östra gren.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2338,10 +2337,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120100253</v>
+        <v>120100036</v>
       </c>
       <c r="B16" t="n">
-        <v>84211</v>
+        <v>96175</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2354,34 +2353,35 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3518</v>
+        <v>2569</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2389,10 +2389,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338708</v>
+        <v>338726</v>
       </c>
       <c r="R16" t="n">
-        <v>6433322</v>
+        <v>6433399</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I granskog ca 50-60 m norr om Gäddevadsbäckens östra gren.</t>
+          <t>15 m väster om bäcken.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 39577-2024 artfynd.xlsx
+++ b/artfynd/A 39577-2024 artfynd.xlsx
@@ -1982,10 +1982,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120100182</v>
+        <v>120100010</v>
       </c>
       <c r="B13" t="n">
-        <v>57326</v>
+        <v>96175</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1994,35 +1994,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2030,10 +2034,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338565</v>
+        <v>338736</v>
       </c>
       <c r="R13" t="n">
-        <v>6433423</v>
+        <v>6433400</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2068,17 +2072,13 @@
           <t>2024-09-26</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spillkråkehack vid basen av en tallhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120100076</v>
+        <v>120099930</v>
       </c>
       <c r="B14" t="n">
-        <v>58164</v>
+        <v>90334</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2113,36 +2113,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208250</v>
+        <v>3215</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2150,10 +2148,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338703</v>
+        <v>338721</v>
       </c>
       <c r="R14" t="n">
-        <v>6433399</v>
+        <v>6433368</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2190,7 +2188,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ett fjolårsexemplar hoppade fram relativt nära bäcken. Troligtvis åkergroda att döma av spetsiga nosen, annars vanlig groda.</t>
+          <t>2 m väster om stora stigen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2218,10 +2216,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120100253</v>
+        <v>120099883</v>
       </c>
       <c r="B15" t="n">
-        <v>84211</v>
+        <v>96175</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2234,34 +2232,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3518</v>
+        <v>2569</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2269,10 +2268,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338708</v>
+        <v>338748</v>
       </c>
       <c r="R15" t="n">
-        <v>6433322</v>
+        <v>6433381</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2305,11 +2304,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>I granskog ca 50-60 m norr om Gäddevadsbäckens östra gren.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2457,10 +2451,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120099930</v>
+        <v>120100076</v>
       </c>
       <c r="B17" t="n">
-        <v>90334</v>
+        <v>58164</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2473,34 +2467,36 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3215</v>
+        <v>208250</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2508,10 +2504,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338721</v>
+        <v>338703</v>
       </c>
       <c r="R17" t="n">
-        <v>6433368</v>
+        <v>6433399</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2548,7 +2544,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2 m väster om stora stigen.</t>
+          <t>Ett fjolårsexemplar hoppade fram relativt nära bäcken. Troligtvis åkergroda att döma av spetsiga nosen, annars vanlig groda.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2576,10 +2572,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120100010</v>
+        <v>120100253</v>
       </c>
       <c r="B18" t="n">
-        <v>96175</v>
+        <v>84211</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2592,35 +2588,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2569</v>
+        <v>3518</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2628,10 +2623,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338736</v>
+        <v>338708</v>
       </c>
       <c r="R18" t="n">
-        <v>6433400</v>
+        <v>6433322</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2664,6 +2659,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>I granskog ca 50-60 m norr om Gäddevadsbäckens östra gren.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2691,10 +2691,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120099883</v>
+        <v>120100182</v>
       </c>
       <c r="B19" t="n">
-        <v>96175</v>
+        <v>57326</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2703,39 +2703,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2743,10 +2739,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>338748</v>
+        <v>338565</v>
       </c>
       <c r="R19" t="n">
-        <v>6433381</v>
+        <v>6433423</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2781,13 +2777,17 @@
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spillkråkehack vid basen av en tallhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39577-2024 artfynd.xlsx
+++ b/artfynd/A 39577-2024 artfynd.xlsx
@@ -1982,10 +1982,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120100010</v>
+        <v>120100182</v>
       </c>
       <c r="B13" t="n">
-        <v>96175</v>
+        <v>57326</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1994,39 +1994,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2034,10 +2030,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338736</v>
+        <v>338565</v>
       </c>
       <c r="R13" t="n">
-        <v>6433400</v>
+        <v>6433423</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2072,13 +2068,17 @@
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillkråkehack vid basen av en tallhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120099930</v>
+        <v>120100010</v>
       </c>
       <c r="B14" t="n">
-        <v>90334</v>
+        <v>96175</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2113,34 +2113,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3215</v>
+        <v>2569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2148,10 +2149,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338721</v>
+        <v>338736</v>
       </c>
       <c r="R14" t="n">
-        <v>6433368</v>
+        <v>6433400</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2184,11 +2185,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2 m väster om stora stigen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2216,10 +2212,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120099883</v>
+        <v>120100076</v>
       </c>
       <c r="B15" t="n">
-        <v>96175</v>
+        <v>58164</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2232,35 +2228,36 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2569</v>
+        <v>208250</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2268,10 +2265,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338748</v>
+        <v>338703</v>
       </c>
       <c r="R15" t="n">
-        <v>6433381</v>
+        <v>6433399</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2304,6 +2301,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ett fjolårsexemplar hoppade fram relativt nära bäcken. Troligtvis åkergroda att döma av spetsiga nosen, annars vanlig groda.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2331,10 +2333,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120100036</v>
+        <v>120100253</v>
       </c>
       <c r="B16" t="n">
-        <v>96175</v>
+        <v>84211</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2347,35 +2349,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2569</v>
+        <v>3518</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2383,10 +2384,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338726</v>
+        <v>338708</v>
       </c>
       <c r="R16" t="n">
-        <v>6433399</v>
+        <v>6433322</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2423,7 +2424,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>15 m väster om bäcken.</t>
+          <t>I granskog ca 50-60 m norr om Gäddevadsbäckens östra gren.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2451,10 +2452,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120100076</v>
+        <v>120099930</v>
       </c>
       <c r="B17" t="n">
-        <v>58164</v>
+        <v>90334</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2467,36 +2468,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>208250</v>
+        <v>3215</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2504,10 +2503,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338703</v>
+        <v>338721</v>
       </c>
       <c r="R17" t="n">
-        <v>6433399</v>
+        <v>6433368</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2544,7 +2543,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ett fjolårsexemplar hoppade fram relativt nära bäcken. Troligtvis åkergroda att döma av spetsiga nosen, annars vanlig groda.</t>
+          <t>2 m väster om stora stigen.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2572,10 +2571,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120100253</v>
+        <v>120100036</v>
       </c>
       <c r="B18" t="n">
-        <v>84211</v>
+        <v>96175</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2588,34 +2587,35 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3518</v>
+        <v>2569</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338708</v>
+        <v>338726</v>
       </c>
       <c r="R18" t="n">
-        <v>6433322</v>
+        <v>6433399</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I granskog ca 50-60 m norr om Gäddevadsbäckens östra gren.</t>
+          <t>15 m väster om bäcken.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2691,10 +2691,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120100182</v>
+        <v>120099883</v>
       </c>
       <c r="B19" t="n">
-        <v>57326</v>
+        <v>96175</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2703,35 +2703,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2739,10 +2743,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>338565</v>
+        <v>338748</v>
       </c>
       <c r="R19" t="n">
-        <v>6433423</v>
+        <v>6433381</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2777,17 +2781,13 @@
           <t>2024-09-26</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Spillkråkehack vid basen av en tallhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39577-2024 artfynd.xlsx
+++ b/artfynd/A 39577-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2804,6 +2804,116 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120338711</v>
+      </c>
+      <c r="B20" t="n">
+        <v>84228</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3518</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Smal svampklubba</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tolypocladium ophioglossoides</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Risveden/Gäddevadsbäcken, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>338737</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6433311</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39577-2024 artfynd.xlsx
+++ b/artfynd/A 39577-2024 artfynd.xlsx
@@ -1982,10 +1982,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120100182</v>
+        <v>120100036</v>
       </c>
       <c r="B13" t="n">
-        <v>57326</v>
+        <v>96198</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1994,35 +1994,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2030,10 +2034,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338565</v>
+        <v>338726</v>
       </c>
       <c r="R13" t="n">
-        <v>6433423</v>
+        <v>6433399</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2070,7 +2074,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen av en tallhögstubbe.</t>
+          <t>15 m väster om bäcken.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2079,6 +2083,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2097,10 +2102,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120100010</v>
+        <v>120099883</v>
       </c>
       <c r="B14" t="n">
-        <v>96175</v>
+        <v>96198</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2132,7 +2137,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2149,10 +2154,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338736</v>
+        <v>338748</v>
       </c>
       <c r="R14" t="n">
-        <v>6433400</v>
+        <v>6433381</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2215,7 +2220,7 @@
         <v>120100076</v>
       </c>
       <c r="B15" t="n">
-        <v>58164</v>
+        <v>58174</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2333,10 +2338,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120100253</v>
+        <v>120099930</v>
       </c>
       <c r="B16" t="n">
-        <v>84211</v>
+        <v>90351</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2349,21 +2354,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3518</v>
+        <v>3215</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2384,10 +2389,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338708</v>
+        <v>338721</v>
       </c>
       <c r="R16" t="n">
-        <v>6433322</v>
+        <v>6433368</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2424,7 +2429,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I granskog ca 50-60 m norr om Gäddevadsbäckens östra gren.</t>
+          <t>2 m väster om stora stigen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2452,10 +2457,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120099930</v>
+        <v>120100010</v>
       </c>
       <c r="B17" t="n">
-        <v>90334</v>
+        <v>96198</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2468,34 +2473,35 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3215</v>
+        <v>2569</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2503,10 +2509,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338721</v>
+        <v>338736</v>
       </c>
       <c r="R17" t="n">
-        <v>6433368</v>
+        <v>6433400</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2539,11 +2545,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2 m väster om stora stigen.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2571,10 +2572,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120100036</v>
+        <v>120100253</v>
       </c>
       <c r="B18" t="n">
-        <v>96175</v>
+        <v>84228</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2587,35 +2588,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2569</v>
+        <v>3518</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338726</v>
+        <v>338708</v>
       </c>
       <c r="R18" t="n">
-        <v>6433399</v>
+        <v>6433322</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>15 m väster om bäcken.</t>
+          <t>I granskog ca 50-60 m norr om Gäddevadsbäckens östra gren.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2691,10 +2691,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120099883</v>
+        <v>120100182</v>
       </c>
       <c r="B19" t="n">
-        <v>96175</v>
+        <v>57336</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2703,39 +2703,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2743,10 +2739,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>338748</v>
+        <v>338565</v>
       </c>
       <c r="R19" t="n">
-        <v>6433381</v>
+        <v>6433423</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2781,13 +2777,17 @@
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spillkråkehack vid basen av en tallhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39577-2024 artfynd.xlsx
+++ b/artfynd/A 39577-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2914,6 +2914,238 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120372302</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91872</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>338606</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6433440</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Flertalet kluster intill rotig jordvall Äldre skogsbetad barrblandskog</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120372307</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91872</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gäddevadsbäcken / Mickelsdamm , Vg</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>338722</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6433351</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Flertalet kluster växer I jordvall i tidigare skogsbetad skog.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39577-2024 artfynd.xlsx
+++ b/artfynd/A 39577-2024 artfynd.xlsx
@@ -1982,10 +1982,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120100036</v>
+        <v>120100182</v>
       </c>
       <c r="B13" t="n">
-        <v>96198</v>
+        <v>57336</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1994,39 +1994,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2034,10 +2030,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338726</v>
+        <v>338565</v>
       </c>
       <c r="R13" t="n">
-        <v>6433399</v>
+        <v>6433423</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2074,7 +2070,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>15 m väster om bäcken.</t>
+          <t>Spillkråkehack vid basen av en tallhögstubbe.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2083,7 +2079,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2102,10 +2097,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120099883</v>
+        <v>120099930</v>
       </c>
       <c r="B14" t="n">
-        <v>96198</v>
+        <v>90351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2118,35 +2113,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2569</v>
+        <v>3215</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2154,10 +2148,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338748</v>
+        <v>338721</v>
       </c>
       <c r="R14" t="n">
-        <v>6433381</v>
+        <v>6433368</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2190,6 +2184,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2 m väster om stora stigen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2217,10 +2216,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120100076</v>
+        <v>120100010</v>
       </c>
       <c r="B15" t="n">
-        <v>58174</v>
+        <v>96198</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2233,36 +2232,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208250</v>
+        <v>2569</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2270,10 +2268,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338703</v>
+        <v>338736</v>
       </c>
       <c r="R15" t="n">
-        <v>6433399</v>
+        <v>6433400</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2306,11 +2304,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ett fjolårsexemplar hoppade fram relativt nära bäcken. Troligtvis åkergroda att döma av spetsiga nosen, annars vanlig groda.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2338,10 +2331,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120099930</v>
+        <v>120100076</v>
       </c>
       <c r="B16" t="n">
-        <v>90351</v>
+        <v>58174</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2354,34 +2347,36 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3215</v>
+        <v>208250</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2389,10 +2384,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338721</v>
+        <v>338703</v>
       </c>
       <c r="R16" t="n">
-        <v>6433368</v>
+        <v>6433399</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2429,7 +2424,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2 m väster om stora stigen.</t>
+          <t>Ett fjolårsexemplar hoppade fram relativt nära bäcken. Troligtvis åkergroda att döma av spetsiga nosen, annars vanlig groda.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2457,7 +2452,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120100010</v>
+        <v>120099883</v>
       </c>
       <c r="B17" t="n">
         <v>96198</v>
@@ -2492,7 +2487,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2509,10 +2504,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338736</v>
+        <v>338748</v>
       </c>
       <c r="R17" t="n">
-        <v>6433400</v>
+        <v>6433381</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2691,10 +2686,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120100182</v>
+        <v>120100036</v>
       </c>
       <c r="B19" t="n">
-        <v>57336</v>
+        <v>96198</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2703,35 +2698,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2739,10 +2738,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>338565</v>
+        <v>338726</v>
       </c>
       <c r="R19" t="n">
-        <v>6433423</v>
+        <v>6433399</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2779,7 +2778,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen av en tallhögstubbe.</t>
+          <t>15 m väster om bäcken.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2788,6 +2787,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2916,7 +2916,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120372302</v>
+        <v>120372307</v>
       </c>
       <c r="B21" t="n">
         <v>91872</v>
@@ -2947,7 +2947,7 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -2955,14 +2955,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mickelsdamm Skår, Vg</t>
+          <t>Gäddevadsbäcken / Mickelsdamm , Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>338606</v>
+        <v>338722</v>
       </c>
       <c r="R21" t="n">
-        <v>6433440</v>
+        <v>6433351</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2989,17 +2989,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Flertalet kluster intill rotig jordvall Äldre skogsbetad barrblandskog</t>
+          <t>Flertalet kluster växer I jordvall i tidigare skogsbetad skog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3032,7 +3032,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120372307</v>
+        <v>120372302</v>
       </c>
       <c r="B22" t="n">
         <v>91872</v>
@@ -3063,7 +3063,7 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -3071,14 +3071,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken / Mickelsdamm , Vg</t>
+          <t>Mickelsdamm Skår, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>338722</v>
+        <v>338606</v>
       </c>
       <c r="R22" t="n">
-        <v>6433351</v>
+        <v>6433440</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3105,17 +3105,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Flertalet kluster växer I jordvall i tidigare skogsbetad skog.</t>
+          <t>Flertalet kluster intill rotig jordvall Äldre skogsbetad barrblandskog</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 39577-2024 artfynd.xlsx
+++ b/artfynd/A 39577-2024 artfynd.xlsx
@@ -2097,10 +2097,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120099930</v>
+        <v>120099883</v>
       </c>
       <c r="B14" t="n">
-        <v>90351</v>
+        <v>96198</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2113,34 +2113,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3215</v>
+        <v>2569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2148,10 +2149,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338721</v>
+        <v>338748</v>
       </c>
       <c r="R14" t="n">
-        <v>6433368</v>
+        <v>6433381</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2184,11 +2185,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2 m väster om stora stigen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2216,10 +2212,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120100010</v>
+        <v>120100253</v>
       </c>
       <c r="B15" t="n">
-        <v>96198</v>
+        <v>84228</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2232,35 +2228,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2569</v>
+        <v>3518</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2268,10 +2263,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338736</v>
+        <v>338708</v>
       </c>
       <c r="R15" t="n">
-        <v>6433400</v>
+        <v>6433322</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2304,6 +2299,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>I granskog ca 50-60 m norr om Gäddevadsbäckens östra gren.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2331,10 +2331,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120100076</v>
+        <v>120100010</v>
       </c>
       <c r="B16" t="n">
-        <v>58174</v>
+        <v>96198</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2347,36 +2347,35 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208250</v>
+        <v>2569</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2384,10 +2383,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338703</v>
+        <v>338736</v>
       </c>
       <c r="R16" t="n">
-        <v>6433399</v>
+        <v>6433400</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2420,11 +2419,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ett fjolårsexemplar hoppade fram relativt nära bäcken. Troligtvis åkergroda att döma av spetsiga nosen, annars vanlig groda.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2452,10 +2446,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120099883</v>
+        <v>120099930</v>
       </c>
       <c r="B17" t="n">
-        <v>96198</v>
+        <v>90351</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2468,35 +2462,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2569</v>
+        <v>3215</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2504,10 +2497,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338748</v>
+        <v>338721</v>
       </c>
       <c r="R17" t="n">
-        <v>6433381</v>
+        <v>6433368</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2540,6 +2533,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2 m väster om stora stigen.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2567,10 +2565,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120100253</v>
+        <v>120100076</v>
       </c>
       <c r="B18" t="n">
-        <v>84228</v>
+        <v>58174</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2583,34 +2581,36 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3518</v>
+        <v>208250</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2618,10 +2618,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338708</v>
+        <v>338703</v>
       </c>
       <c r="R18" t="n">
-        <v>6433322</v>
+        <v>6433399</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I granskog ca 50-60 m norr om Gäddevadsbäckens östra gren.</t>
+          <t>Ett fjolårsexemplar hoppade fram relativt nära bäcken. Troligtvis åkergroda att döma av spetsiga nosen, annars vanlig groda.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 39577-2024 artfynd.xlsx
+++ b/artfynd/A 39577-2024 artfynd.xlsx
@@ -1385,7 +1385,7 @@
         <v>111144195</v>
       </c>
       <c r="B8" t="n">
-        <v>88597</v>
+        <v>89759</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338767.8169904748</v>
+        <v>338768</v>
       </c>
       <c r="R8" t="n">
-        <v>6433411.705786019</v>
+        <v>6433412</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1462,19 +1462,9 @@
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 39577-2024 artfynd.xlsx
+++ b/artfynd/A 39577-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1972,10 +1972,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120100182</v>
+        <v>120100036</v>
       </c>
       <c r="B13" t="n">
-        <v>57336</v>
+        <v>96198</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1984,35 +1984,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2020,10 +2024,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338565</v>
+        <v>338726</v>
       </c>
       <c r="R13" t="n">
-        <v>6433423</v>
+        <v>6433399</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2060,7 +2064,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen av en tallhögstubbe.</t>
+          <t>15 m väster om bäcken.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2069,6 +2073,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2087,10 +2092,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120099883</v>
+        <v>120099930</v>
       </c>
       <c r="B14" t="n">
-        <v>96198</v>
+        <v>90351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2103,35 +2108,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2569</v>
+        <v>3215</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2139,10 +2143,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338748</v>
+        <v>338721</v>
       </c>
       <c r="R14" t="n">
-        <v>6433381</v>
+        <v>6433368</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2175,6 +2179,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2 m väster om stora stigen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2202,10 +2211,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120100253</v>
+        <v>120099883</v>
       </c>
       <c r="B15" t="n">
-        <v>84228</v>
+        <v>96198</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2218,34 +2227,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3518</v>
+        <v>2569</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2253,10 +2263,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338708</v>
+        <v>338748</v>
       </c>
       <c r="R15" t="n">
-        <v>6433322</v>
+        <v>6433381</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2289,11 +2299,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>I granskog ca 50-60 m norr om Gäddevadsbäckens östra gren.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2321,10 +2326,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120100010</v>
+        <v>120100076</v>
       </c>
       <c r="B16" t="n">
-        <v>96198</v>
+        <v>58174</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2337,35 +2342,36 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2569</v>
+        <v>208250</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2373,10 +2379,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338736</v>
+        <v>338703</v>
       </c>
       <c r="R16" t="n">
-        <v>6433400</v>
+        <v>6433399</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2409,6 +2415,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ett fjolårsexemplar hoppade fram relativt nära bäcken. Troligtvis åkergroda att döma av spetsiga nosen, annars vanlig groda.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2436,10 +2447,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120099930</v>
+        <v>120100253</v>
       </c>
       <c r="B17" t="n">
-        <v>90351</v>
+        <v>84228</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2452,21 +2463,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3215</v>
+        <v>3518</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2487,10 +2498,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338721</v>
+        <v>338708</v>
       </c>
       <c r="R17" t="n">
-        <v>6433368</v>
+        <v>6433322</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2527,7 +2538,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2 m väster om stora stigen.</t>
+          <t>I granskog ca 50-60 m norr om Gäddevadsbäckens östra gren.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2555,10 +2566,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120100076</v>
+        <v>120100182</v>
       </c>
       <c r="B18" t="n">
-        <v>58174</v>
+        <v>57336</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2567,40 +2578,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>208250</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2608,10 +2614,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338703</v>
+        <v>338565</v>
       </c>
       <c r="R18" t="n">
-        <v>6433399</v>
+        <v>6433423</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2648,7 +2654,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ett fjolårsexemplar hoppade fram relativt nära bäcken. Troligtvis åkergroda att döma av spetsiga nosen, annars vanlig groda.</t>
+          <t>Spillkråkehack vid basen av en tallhögstubbe.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2657,7 +2663,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2676,7 +2681,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120100036</v>
+        <v>120100010</v>
       </c>
       <c r="B19" t="n">
         <v>96198</v>
@@ -2711,12 +2716,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2728,10 +2733,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>338726</v>
+        <v>338736</v>
       </c>
       <c r="R19" t="n">
-        <v>6433399</v>
+        <v>6433400</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2764,11 +2769,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>15 m väster om bäcken.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2906,7 +2906,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120372307</v>
+        <v>120372302</v>
       </c>
       <c r="B21" t="n">
         <v>91872</v>
@@ -2937,7 +2937,7 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -2945,14 +2945,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken / Mickelsdamm , Vg</t>
+          <t>Mickelsdamm Skår, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>338722</v>
+        <v>338606</v>
       </c>
       <c r="R21" t="n">
-        <v>6433351</v>
+        <v>6433440</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2979,17 +2979,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Flertalet kluster växer I jordvall i tidigare skogsbetad skog.</t>
+          <t>Flertalet kluster intill rotig jordvall Äldre skogsbetad barrblandskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3022,7 +3022,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120372302</v>
+        <v>120372307</v>
       </c>
       <c r="B22" t="n">
         <v>91872</v>
@@ -3053,7 +3053,7 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -3061,14 +3061,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mickelsdamm Skår, Vg</t>
+          <t>Gäddevadsbäcken / Mickelsdamm , Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>338606</v>
+        <v>338722</v>
       </c>
       <c r="R22" t="n">
-        <v>6433440</v>
+        <v>6433351</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3095,17 +3095,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Flertalet kluster intill rotig jordvall Äldre skogsbetad barrblandskog</t>
+          <t>Flertalet kluster växer I jordvall i tidigare skogsbetad skog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3135,6 +3135,131 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120388678</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>338641</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6433397</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Växer på bergsåsen intill tallar</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Bergsås i äldre skogsbetad barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva, Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39577-2024 artfynd.xlsx
+++ b/artfynd/A 39577-2024 artfynd.xlsx
@@ -1972,10 +1972,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120100036</v>
+        <v>120099930</v>
       </c>
       <c r="B13" t="n">
-        <v>96198</v>
+        <v>90351</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1988,35 +1988,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>3215</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2024,10 +2023,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338726</v>
+        <v>338721</v>
       </c>
       <c r="R13" t="n">
-        <v>6433399</v>
+        <v>6433368</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2064,7 +2063,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>15 m väster om bäcken.</t>
+          <t>2 m väster om stora stigen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2092,10 +2091,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120099930</v>
+        <v>120100253</v>
       </c>
       <c r="B14" t="n">
-        <v>90351</v>
+        <v>84228</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2108,21 +2107,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3215</v>
+        <v>3518</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2143,10 +2142,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338721</v>
+        <v>338708</v>
       </c>
       <c r="R14" t="n">
-        <v>6433368</v>
+        <v>6433322</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2183,7 +2182,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2 m väster om stora stigen.</t>
+          <t>I granskog ca 50-60 m norr om Gäddevadsbäckens östra gren.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2211,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120099883</v>
+        <v>120100182</v>
       </c>
       <c r="B15" t="n">
-        <v>96198</v>
+        <v>57336</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2223,39 +2222,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2263,10 +2258,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338748</v>
+        <v>338565</v>
       </c>
       <c r="R15" t="n">
-        <v>6433381</v>
+        <v>6433423</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2301,13 +2296,17 @@
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spillkråkehack vid basen av en tallhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2326,10 +2325,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120100076</v>
+        <v>120100010</v>
       </c>
       <c r="B16" t="n">
-        <v>58174</v>
+        <v>96198</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2342,36 +2341,35 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208250</v>
+        <v>2569</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2379,10 +2377,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338703</v>
+        <v>338736</v>
       </c>
       <c r="R16" t="n">
-        <v>6433399</v>
+        <v>6433400</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2415,11 +2413,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ett fjolårsexemplar hoppade fram relativt nära bäcken. Troligtvis åkergroda att döma av spetsiga nosen, annars vanlig groda.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2447,10 +2440,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120100253</v>
+        <v>120100076</v>
       </c>
       <c r="B17" t="n">
-        <v>84228</v>
+        <v>58174</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2463,34 +2456,36 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3518</v>
+        <v>208250</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2498,10 +2493,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338708</v>
+        <v>338703</v>
       </c>
       <c r="R17" t="n">
-        <v>6433322</v>
+        <v>6433399</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2538,7 +2533,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>I granskog ca 50-60 m norr om Gäddevadsbäckens östra gren.</t>
+          <t>Ett fjolårsexemplar hoppade fram relativt nära bäcken. Troligtvis åkergroda att döma av spetsiga nosen, annars vanlig groda.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2566,10 +2561,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120100182</v>
+        <v>120100036</v>
       </c>
       <c r="B18" t="n">
-        <v>57336</v>
+        <v>96198</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2578,35 +2573,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2614,10 +2613,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338565</v>
+        <v>338726</v>
       </c>
       <c r="R18" t="n">
-        <v>6433423</v>
+        <v>6433399</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2654,7 +2653,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen av en tallhögstubbe.</t>
+          <t>15 m väster om bäcken.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2663,6 +2662,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2681,7 +2681,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120100010</v>
+        <v>120099883</v>
       </c>
       <c r="B19" t="n">
         <v>96198</v>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>338736</v>
+        <v>338748</v>
       </c>
       <c r="R19" t="n">
-        <v>6433400</v>
+        <v>6433381</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>

--- a/artfynd/A 39577-2024 artfynd.xlsx
+++ b/artfynd/A 39577-2024 artfynd.xlsx
@@ -2091,10 +2091,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120100253</v>
+        <v>120100182</v>
       </c>
       <c r="B14" t="n">
-        <v>84228</v>
+        <v>57336</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2103,38 +2103,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3518</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2142,10 +2139,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338708</v>
+        <v>338565</v>
       </c>
       <c r="R14" t="n">
-        <v>6433322</v>
+        <v>6433423</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2182,7 +2179,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>I granskog ca 50-60 m norr om Gäddevadsbäckens östra gren.</t>
+          <t>Spillkråkehack vid basen av en tallhögstubbe.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2191,7 +2188,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2210,10 +2206,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120100182</v>
+        <v>120100253</v>
       </c>
       <c r="B15" t="n">
-        <v>57336</v>
+        <v>84228</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2222,35 +2218,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>3518</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2258,10 +2257,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338565</v>
+        <v>338708</v>
       </c>
       <c r="R15" t="n">
-        <v>6433423</v>
+        <v>6433322</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2298,7 +2297,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen av en tallhögstubbe.</t>
+          <t>I granskog ca 50-60 m norr om Gäddevadsbäckens östra gren.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2307,6 +2306,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39577-2024 artfynd.xlsx
+++ b/artfynd/A 39577-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1972,10 +1972,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120099930</v>
+        <v>120099883</v>
       </c>
       <c r="B13" t="n">
-        <v>90351</v>
+        <v>96198</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1988,34 +1988,35 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3215</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2023,10 +2024,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338721</v>
+        <v>338748</v>
       </c>
       <c r="R13" t="n">
-        <v>6433368</v>
+        <v>6433381</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2059,11 +2060,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2 m väster om stora stigen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2091,10 +2087,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120100182</v>
+        <v>120099930</v>
       </c>
       <c r="B14" t="n">
-        <v>57336</v>
+        <v>90351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2103,35 +2099,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2139,10 +2138,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338565</v>
+        <v>338721</v>
       </c>
       <c r="R14" t="n">
-        <v>6433423</v>
+        <v>6433368</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2179,7 +2178,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen av en tallhögstubbe.</t>
+          <t>2 m väster om stora stigen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2188,6 +2187,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2206,10 +2206,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120100253</v>
+        <v>120100182</v>
       </c>
       <c r="B15" t="n">
-        <v>84228</v>
+        <v>57336</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2218,38 +2218,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3518</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2257,10 +2254,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338708</v>
+        <v>338565</v>
       </c>
       <c r="R15" t="n">
-        <v>6433322</v>
+        <v>6433423</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2297,7 +2294,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>I granskog ca 50-60 m norr om Gäddevadsbäckens östra gren.</t>
+          <t>Spillkråkehack vid basen av en tallhögstubbe.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,7 +2303,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2440,10 +2436,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120100076</v>
+        <v>120100036</v>
       </c>
       <c r="B17" t="n">
-        <v>58174</v>
+        <v>96198</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2456,36 +2452,35 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>208250</v>
+        <v>2569</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2493,7 +2488,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338703</v>
+        <v>338726</v>
       </c>
       <c r="R17" t="n">
         <v>6433399</v>
@@ -2533,7 +2528,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ett fjolårsexemplar hoppade fram relativt nära bäcken. Troligtvis åkergroda att döma av spetsiga nosen, annars vanlig groda.</t>
+          <t>15 m väster om bäcken.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2561,10 +2556,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120100036</v>
+        <v>120100076</v>
       </c>
       <c r="B18" t="n">
-        <v>96198</v>
+        <v>58174</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2577,35 +2572,36 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2569</v>
+        <v>208250</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2613,7 +2609,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338726</v>
+        <v>338703</v>
       </c>
       <c r="R18" t="n">
         <v>6433399</v>
@@ -2653,7 +2649,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>15 m väster om bäcken.</t>
+          <t>Ett fjolårsexemplar hoppade fram relativt nära bäcken. Troligtvis åkergroda att döma av spetsiga nosen, annars vanlig groda.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2681,10 +2677,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120099883</v>
+        <v>120100253</v>
       </c>
       <c r="B19" t="n">
-        <v>96198</v>
+        <v>84228</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2697,35 +2693,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2569</v>
+        <v>3518</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2733,10 +2728,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>338748</v>
+        <v>338708</v>
       </c>
       <c r="R19" t="n">
-        <v>6433381</v>
+        <v>6433322</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2769,6 +2764,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>I granskog ca 50-60 m norr om Gäddevadsbäckens östra gren.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3136,131 +3136,6 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>120388678</v>
-      </c>
-      <c r="B23" t="n">
-        <v>91881</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>5966</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Mickelsdamm Skår, Vg</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>338641</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6433397</v>
-      </c>
-      <c r="S23" t="n">
-        <v>5</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Ale</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Skepplanda</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Växer på bergsåsen intill tallar</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Bergsås i äldre skogsbetad barrblandskog</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Grimhild Angertuva</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Grimhild Angertuva, Liv Vikingson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39577-2024 artfynd.xlsx
+++ b/artfynd/A 39577-2024 artfynd.xlsx
@@ -1972,10 +1972,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120099883</v>
+        <v>120100182</v>
       </c>
       <c r="B13" t="n">
-        <v>96198</v>
+        <v>57336</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1984,39 +1984,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2024,10 +2020,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338748</v>
+        <v>338565</v>
       </c>
       <c r="R13" t="n">
-        <v>6433381</v>
+        <v>6433423</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2062,13 +2058,17 @@
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillkråkehack vid basen av en tallhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2087,10 +2087,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120099930</v>
+        <v>120099883</v>
       </c>
       <c r="B14" t="n">
-        <v>90351</v>
+        <v>96198</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2103,34 +2103,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3215</v>
+        <v>2569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2138,10 +2139,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338721</v>
+        <v>338748</v>
       </c>
       <c r="R14" t="n">
-        <v>6433368</v>
+        <v>6433381</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2174,11 +2175,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2 m väster om stora stigen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2206,10 +2202,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120100182</v>
+        <v>120099930</v>
       </c>
       <c r="B15" t="n">
-        <v>57336</v>
+        <v>90351</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2218,35 +2214,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2254,10 +2253,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338565</v>
+        <v>338721</v>
       </c>
       <c r="R15" t="n">
-        <v>6433423</v>
+        <v>6433368</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2294,7 +2293,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen av en tallhögstubbe.</t>
+          <t>2 m väster om stora stigen.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,6 +2302,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2436,10 +2436,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120100036</v>
+        <v>120100253</v>
       </c>
       <c r="B17" t="n">
-        <v>96198</v>
+        <v>84228</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2452,35 +2452,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2569</v>
+        <v>3518</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2488,10 +2487,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338726</v>
+        <v>338708</v>
       </c>
       <c r="R17" t="n">
-        <v>6433399</v>
+        <v>6433322</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2528,7 +2527,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>15 m väster om bäcken.</t>
+          <t>I granskog ca 50-60 m norr om Gäddevadsbäckens östra gren.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2556,10 +2555,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120100076</v>
+        <v>120100036</v>
       </c>
       <c r="B18" t="n">
-        <v>58174</v>
+        <v>96198</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2572,36 +2571,35 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>208250</v>
+        <v>2569</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2609,7 +2607,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338703</v>
+        <v>338726</v>
       </c>
       <c r="R18" t="n">
         <v>6433399</v>
@@ -2649,7 +2647,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ett fjolårsexemplar hoppade fram relativt nära bäcken. Troligtvis åkergroda att döma av spetsiga nosen, annars vanlig groda.</t>
+          <t>15 m väster om bäcken.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2677,10 +2675,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120100253</v>
+        <v>120100076</v>
       </c>
       <c r="B19" t="n">
-        <v>84228</v>
+        <v>58174</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2693,34 +2691,36 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3518</v>
+        <v>208250</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>338708</v>
+        <v>338703</v>
       </c>
       <c r="R19" t="n">
-        <v>6433322</v>
+        <v>6433399</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>I granskog ca 50-60 m norr om Gäddevadsbäckens östra gren.</t>
+          <t>Ett fjolårsexemplar hoppade fram relativt nära bäcken. Troligtvis åkergroda att döma av spetsiga nosen, annars vanlig groda.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2906,7 +2906,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120372302</v>
+        <v>120372307</v>
       </c>
       <c r="B21" t="n">
         <v>91872</v>
@@ -2937,7 +2937,7 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -2945,14 +2945,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mickelsdamm Skår, Vg</t>
+          <t>Gäddevadsbäcken / Mickelsdamm , Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>338606</v>
+        <v>338722</v>
       </c>
       <c r="R21" t="n">
-        <v>6433440</v>
+        <v>6433351</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2979,17 +2979,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Flertalet kluster intill rotig jordvall Äldre skogsbetad barrblandskog</t>
+          <t>Flertalet kluster växer I jordvall i tidigare skogsbetad skog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3022,7 +3022,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120372307</v>
+        <v>120372302</v>
       </c>
       <c r="B22" t="n">
         <v>91872</v>
@@ -3053,7 +3053,7 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -3061,14 +3061,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken / Mickelsdamm , Vg</t>
+          <t>Mickelsdamm Skår, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>338722</v>
+        <v>338606</v>
       </c>
       <c r="R22" t="n">
-        <v>6433351</v>
+        <v>6433440</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3095,17 +3095,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Flertalet kluster växer I jordvall i tidigare skogsbetad skog.</t>
+          <t>Flertalet kluster intill rotig jordvall Äldre skogsbetad barrblandskog</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 39577-2024 artfynd.xlsx
+++ b/artfynd/A 39577-2024 artfynd.xlsx
@@ -4576,7 +4576,7 @@
         <v>120841831</v>
       </c>
       <c r="B35" t="n">
-        <v>57501</v>
+        <v>57504</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>121181763</v>
       </c>
       <c r="B36" t="n">
-        <v>97017</v>
+        <v>97027</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 39577-2024 artfynd.xlsx
+++ b/artfynd/A 39577-2024 artfynd.xlsx
@@ -4695,7 +4695,7 @@
         <v>121181763</v>
       </c>
       <c r="B36" t="n">
-        <v>97027</v>
+        <v>97040</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 39577-2024 artfynd.xlsx
+++ b/artfynd/A 39577-2024 artfynd.xlsx
@@ -4695,7 +4695,7 @@
         <v>121181763</v>
       </c>
       <c r="B36" t="n">
-        <v>97040</v>
+        <v>97041</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 39577-2024 artfynd.xlsx
+++ b/artfynd/A 39577-2024 artfynd.xlsx
@@ -4695,7 +4695,7 @@
         <v>121181763</v>
       </c>
       <c r="B36" t="n">
-        <v>97041</v>
+        <v>97044</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 39577-2024 artfynd.xlsx
+++ b/artfynd/A 39577-2024 artfynd.xlsx
@@ -4695,7 +4695,7 @@
         <v>121181763</v>
       </c>
       <c r="B36" t="n">
-        <v>97044</v>
+        <v>97050</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 39577-2024 artfynd.xlsx
+++ b/artfynd/A 39577-2024 artfynd.xlsx
@@ -4695,7 +4695,7 @@
         <v>121181763</v>
       </c>
       <c r="B36" t="n">
-        <v>97050</v>
+        <v>97051</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 39577-2024 artfynd.xlsx
+++ b/artfynd/A 39577-2024 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98803568</v>
+        <v>98803563</v>
       </c>
       <c r="B3" t="n">
-        <v>96602</v>
+        <v>96610</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98803563</v>
+        <v>110371770</v>
       </c>
       <c r="B4" t="n">
-        <v>96610</v>
+        <v>5135</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,38 +915,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken, Vg</t>
+          <t>Angertuvan, öster om, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338634</v>
+        <v>338585.336111301</v>
       </c>
       <c r="R4" t="n">
-        <v>6433326</v>
+        <v>6433367.108660555</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -973,12 +978,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-02-27</t>
+          <t>2023-04-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-02-27</t>
+          <t>2023-04-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Grov död gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,19 +1014,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110371770</v>
+        <v>110371744</v>
       </c>
       <c r="B5" t="n">
         <v>5135</v>
@@ -1055,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338585.336111301</v>
+        <v>338607.2757862964</v>
       </c>
       <c r="R5" t="n">
-        <v>6433367.108660555</v>
+        <v>6433357.734230375</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1105,7 +1125,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Grov död gran.</t>
+          <t>I senvuxen död gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110371744</v>
+        <v>110370682</v>
       </c>
       <c r="B6" t="n">
-        <v>5135</v>
+        <v>95198</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,32 +1169,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>2606</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1182,13 +1197,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338607.2757862964</v>
+        <v>338804.6224958536</v>
       </c>
       <c r="R6" t="n">
-        <v>6433357.734230375</v>
+        <v>6433309.972010612</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,7 +1227,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-04-10</t>
+          <t>2023-04-09</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1222,7 +1237,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-04-10</t>
+          <t>2023-04-09</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1232,7 +1247,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>I senvuxen död gran.</t>
+          <t>Mycket, på några senvuxna ekar i mindre brant.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110370682</v>
+        <v>111144195</v>
       </c>
       <c r="B7" t="n">
-        <v>95198</v>
+        <v>89839</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,45 +1287,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2606</v>
+        <v>151</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bronssopp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Butyriboletus appendiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Schaeff.) D.Arora &amp; J.L.Frank</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Angertuvan, öster om, Vg</t>
+          <t>Mickelsdamm, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338804.6224958536</v>
+        <v>338768</v>
       </c>
       <c r="R7" t="n">
-        <v>6433309.972010612</v>
+        <v>6433412</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,27 +1352,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-04-09</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-04-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Mycket, på några senvuxna ekar i mindre brant.</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,25 +1370,35 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrskog, gran/tal med inslag av al, asp, ek och hassel</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111144195</v>
+        <v>112431264</v>
       </c>
       <c r="B8" t="n">
-        <v>89839</v>
+        <v>5160</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,48 +1407,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>151</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronssopp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Butyriboletus appendiculatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) D.Arora &amp; J.L.Frank</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mickelsdamm, Vg</t>
+          <t>Gäddevadsbäcken, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338768</v>
+        <v>338730</v>
       </c>
       <c r="R8" t="n">
-        <v>6433412</v>
+        <v>6433393</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1459,12 +1474,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På två senvuxna, döda granar nära bäcken.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,35 +1497,25 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Barrskog, gran/tal med inslag av al, asp, ek och hassel</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112431264</v>
+        <v>112431247</v>
       </c>
       <c r="B9" t="n">
-        <v>5160</v>
+        <v>5182</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,21 +1528,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1551,13 +1561,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338730</v>
+        <v>338720</v>
       </c>
       <c r="R9" t="n">
-        <v>6433393</v>
+        <v>6433370</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1591,7 +1601,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På två senvuxna, döda granar nära bäcken.</t>
+          <t>I gran nära bäck.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112431247</v>
+        <v>115569911</v>
       </c>
       <c r="B10" t="n">
-        <v>5182</v>
+        <v>96602</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,32 +1645,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>224361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1668,13 +1673,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338720</v>
+        <v>338634</v>
       </c>
       <c r="R10" t="n">
-        <v>6433370</v>
+        <v>6433326</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1698,17 +1703,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>I gran nära bäck.</t>
+          <t>Långa blad men ej fint sågtandade. Växte tillsammans med revlummer.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,12 +1729,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Tim Hipkiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Tim Hipkiss</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
